--- a/data/chinese/P2T3_Chapter16.xlsx
+++ b/data/chinese/P2T3_Chapter16.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/Chinese/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/homes/ximonlam/Mac/單詞複習網素材/Chinese/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61A8C2D-18E9-C94F-A70D-30773D631AB9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{871D74CE-ECD0-814D-A08A-BFCB4D95C7F3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,55 +60,61 @@
     <t>波浪滔滔</t>
   </si>
   <si>
-    <t>形容波浪連綿不斷、洶湧翻滾</t>
-  </si>
-  <si>
     <t>大海上波浪滔滔，船隻緩緩前行。</t>
   </si>
   <si>
     <t>暴跳如雷</t>
   </si>
   <si>
-    <t>形容人發怒時大聲吼叫、情緒激動</t>
-  </si>
-  <si>
     <t>聽到這件事，他頓時暴跳如雷。</t>
   </si>
   <si>
     <t>狂怒</t>
   </si>
   <si>
-    <t>極度憤怒</t>
-  </si>
-  <si>
     <t>巨浪翻滾，彷彿大海陷入狂怒之中。</t>
   </si>
   <si>
     <t>歇歇腳</t>
   </si>
   <si>
-    <t>停下腳步休息一會兒</t>
-  </si>
-  <si>
     <t>走了許久，我們找個地方歇歇腳。</t>
   </si>
   <si>
     <t>驚慌</t>
   </si>
   <si>
-    <t>驚恐慌亂，心神不定</t>
-  </si>
-  <si>
     <t>突然的變故讓大家一陣驚慌。</t>
   </si>
   <si>
+    <t>為自己、他人或事物感到光榮與驕傲</t>
+  </si>
+  <si>
+    <t>身為中國人，我感到十分自豪。</t>
+  </si>
+  <si>
+    <t>形容水面上的波浪很大、連綿不斷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>形容人非常生氣，發脾氣的樣子很嚇人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>形容非常、非常生氣，情緒很激動</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>走累了停下來休息一下，讓腳放鬆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>形容很大、很洶湧的波浪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>自豪</t>
-  </si>
-  <si>
-    <t>為自己、他人或事物感到光榮與驕傲</t>
-  </si>
-  <si>
-    <t>身為中國人，我感到十分自豪。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -787,7 +793,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="53.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="64.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="71.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="39.83203125" bestFit="1" customWidth="1"/>
@@ -822,10 +828,10 @@
         <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>9</v>
       </c>
       <c r="D2" s="3">
         <v>1</v>
@@ -834,13 +840,13 @@
     </row>
     <row r="3" spans="1:11" ht="27">
       <c r="A3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>12</v>
       </c>
       <c r="D3" s="3">
         <v>1</v>
@@ -849,13 +855,13 @@
     </row>
     <row r="4" spans="1:11" ht="27">
       <c r="A4" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
@@ -864,13 +870,13 @@
     </row>
     <row r="5" spans="1:11" ht="27">
       <c r="A5" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D5" s="3">
         <v>2</v>
@@ -879,13 +885,13 @@
     </row>
     <row r="6" spans="1:11" ht="27">
       <c r="A6" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D6" s="3">
         <v>2</v>
@@ -894,13 +900,13 @@
     </row>
     <row r="7" spans="1:11" ht="27">
       <c r="A7" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D7" s="3">
         <v>2</v>
